--- a/data/trans_dic/P1002-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 11,86</t>
+          <t>7,96; 11,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 15,31</t>
+          <t>10,98; 15,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 11,28</t>
+          <t>7,02; 11,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 14,14</t>
+          <t>9,19; 14,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,09; 14,79</t>
+          <t>10,99; 14,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,64; 25,39</t>
+          <t>20,58; 25,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,84; 23,38</t>
+          <t>17,81; 23,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,74; 24,65</t>
+          <t>20,01; 24,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 12,84</t>
+          <t>10,34; 13,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 20,34</t>
+          <t>17,2; 20,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,86; 17,55</t>
+          <t>13,89; 17,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,11; 19,77</t>
+          <t>16,09; 19,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,75</t>
+          <t>2,05; 3,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,6</t>
+          <t>3,62; 5,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 5,69</t>
+          <t>3,76; 5,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,65</t>
+          <t>3,05; 5,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,32</t>
+          <t>4,87; 7,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,06</t>
+          <t>8,01; 11,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,81</t>
+          <t>6,41; 8,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 7,99</t>
+          <t>4,87; 8,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,14</t>
+          <t>3,64; 5,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,02</t>
+          <t>5,97; 7,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,81</t>
+          <t>5,3; 6,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,53</t>
+          <t>4,55; 6,53</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,58</t>
+          <t>2,17; 5,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,44</t>
+          <t>1,5; 5,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,83</t>
+          <t>1,6; 4,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,68</t>
+          <t>2,52; 5,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,97</t>
+          <t>2,93; 6,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,12</t>
+          <t>3,32; 7,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,72</t>
+          <t>3,02; 6,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,25</t>
+          <t>5,29; 9,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,52</t>
+          <t>3,01; 5,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,66</t>
+          <t>2,77; 5,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,05</t>
+          <t>2,75; 5,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,82</t>
+          <t>4,22; 6,78</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,02</t>
+          <t>4,48; 6,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,76</t>
+          <t>5,88; 7,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,24</t>
+          <t>4,64; 6,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,38</t>
+          <t>4,11; 6,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 9,52</t>
+          <t>7,53; 9,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,84; 15,18</t>
+          <t>12,92; 15,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 11,79</t>
+          <t>9,72; 11,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 11,14</t>
+          <t>8,1; 11,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,53</t>
+          <t>6,26; 7,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 11,14</t>
+          <t>9,63; 11,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 8,8</t>
+          <t>7,42; 8,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,53</t>
+          <t>6,73; 8,52</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84391; 122392</t>
+          <t>82140; 121778</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103878; 149204</t>
+          <t>106994; 150270</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54813; 85086</t>
+          <t>52932; 85925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46838; 72732</t>
+          <t>47280; 72890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>145849; 194514</t>
+          <t>144543; 191785</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>275864; 339414</t>
+          <t>275082; 340291</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>177442; 232502</t>
+          <t>177190; 230870</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>148834; 185837</t>
+          <t>150845; 186181</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>242165; 301415</t>
+          <t>242619; 305749</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>395838; 470119</t>
+          <t>397460; 470339</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>242483; 306951</t>
+          <t>242854; 304488</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>204366; 250802</t>
+          <t>204078; 251617</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35561; 63540</t>
+          <t>34656; 61949</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70725; 109889</t>
+          <t>71011; 111675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77187; 118229</t>
+          <t>78026; 118469</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71005; 129322</t>
+          <t>69743; 132999</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78337; 116189</t>
+          <t>77271; 117088</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>142331; 194415</t>
+          <t>140829; 194303</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>125245; 175226</t>
+          <t>127464; 175155</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>108789; 178771</t>
+          <t>108943; 178903</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119860; 168728</t>
+          <t>119329; 165842</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>227003; 298261</t>
+          <t>222098; 289403</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>212838; 276663</t>
+          <t>215427; 276784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>199269; 295841</t>
+          <t>205847; 295542</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12093; 30761</t>
+          <t>11990; 31329</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7816; 26194</t>
+          <t>7223; 27102</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8523; 26427</t>
+          <t>8726; 26161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15886; 36704</t>
+          <t>16283; 36402</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14462; 33204</t>
+          <t>13953; 31564</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13229; 32661</t>
+          <t>15206; 34666</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16780; 36879</t>
+          <t>16584; 36209</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35711; 61093</t>
+          <t>34935; 59903</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30784; 56717</t>
+          <t>30899; 56196</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24486; 53157</t>
+          <t>26032; 52161</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28959; 55314</t>
+          <t>30118; 54935</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55363; 89127</t>
+          <t>55198; 88643</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>146413; 197135</t>
+          <t>146756; 198797</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>199284; 265356</t>
+          <t>200811; 262456</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>156442; 210780</t>
+          <t>156583; 209605</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>144411; 220310</t>
+          <t>141847; 214515</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>253234; 321680</t>
+          <t>254321; 320284</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>456083; 539469</t>
+          <t>458937; 543010</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>339432; 416453</t>
+          <t>343280; 417314</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>301583; 406681</t>
+          <t>295723; 405709</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>416591; 501248</t>
+          <t>416760; 498152</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>673897; 776250</t>
+          <t>671626; 780492</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>511555; 608392</t>
+          <t>512918; 607692</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>476932; 606191</t>
+          <t>478279; 605036</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1002-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,8</t>
+          <t>8,15; 12,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 15,42</t>
+          <t>10,81; 15,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,39</t>
+          <t>7,26; 11,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 14,17</t>
+          <t>8,69; 13,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 14,58</t>
+          <t>11,02; 14,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,58; 25,46</t>
+          <t>20,74; 25,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 23,21</t>
+          <t>18,09; 23,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,01; 24,69</t>
+          <t>19,61; 24,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 13,03</t>
+          <t>10,34; 12,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,2; 20,35</t>
+          <t>17,15; 20,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,89; 17,41</t>
+          <t>13,71; 17,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,09; 19,84</t>
+          <t>15,67; 19,22</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,66</t>
+          <t>2,03; 3,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,69</t>
+          <t>3,55; 5,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,71</t>
+          <t>3,71; 5,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,81</t>
+          <t>4,06; 6,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,37</t>
+          <t>4,95; 7,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 11,05</t>
+          <t>8,07; 10,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 8,81</t>
+          <t>6,35; 8,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,0</t>
+          <t>6,82; 8,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,05</t>
+          <t>3,7; 5,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 7,78</t>
+          <t>6,09; 7,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,81</t>
+          <t>5,34; 6,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,53</t>
+          <t>5,65; 7,07</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,68</t>
+          <t>2,3; 5,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,63</t>
+          <t>1,6; 5,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,78</t>
+          <t>1,55; 4,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,63</t>
+          <t>2,39; 5,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,63</t>
+          <t>3,0; 6,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,56</t>
+          <t>2,98; 7,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,59</t>
+          <t>2,84; 6,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,07</t>
+          <t>5,79; 9,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,47</t>
+          <t>3,0; 5,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,55</t>
+          <t>2,71; 5,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,01</t>
+          <t>2,59; 4,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,78</t>
+          <t>4,47; 6,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,07</t>
+          <t>4,53; 6,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,68</t>
+          <t>5,83; 7,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,21</t>
+          <t>4,69; 6,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,22</t>
+          <t>5,06; 6,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 9,48</t>
+          <t>7,59; 9,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,92; 15,28</t>
+          <t>12,75; 15,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 11,81</t>
+          <t>9,64; 11,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,11</t>
+          <t>9,92; 11,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,48</t>
+          <t>6,28; 7,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 11,2</t>
+          <t>9,58; 11,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,79</t>
+          <t>7,5; 8,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 8,52</t>
+          <t>7,77; 8,95</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58575</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>167032</t>
+          <t>178883</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>225606</t>
+          <t>241910</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82140; 121778</t>
+          <t>84054; 125946</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106994; 150270</t>
+          <t>105398; 151245</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52932; 85925</t>
+          <t>54762; 85385</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47280; 72890</t>
+          <t>50233; 76940</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>144543; 191785</t>
+          <t>144873; 195443</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>275082; 340291</t>
+          <t>277261; 339487</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>177190; 230870</t>
+          <t>179931; 233440</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>150845; 186181</t>
+          <t>160886; 198301</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>242619; 305749</t>
+          <t>242722; 304037</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>397460; 470339</t>
+          <t>396358; 474061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>242854; 304488</t>
+          <t>239794; 305159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>204078; 251617</t>
+          <t>219085; 268740</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103871</t>
+          <t>112263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>150521</t>
+          <t>168572</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>254392</t>
+          <t>280835</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34656; 61949</t>
+          <t>34345; 60685</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71011; 111675</t>
+          <t>69723; 109327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78026; 118469</t>
+          <t>76950; 116827</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69743; 132999</t>
+          <t>90463; 137510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77271; 117088</t>
+          <t>78642; 116973</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>140829; 194303</t>
+          <t>141796; 192913</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>127464; 175155</t>
+          <t>126319; 173439</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>108943; 178903</t>
+          <t>148009; 194007</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119329; 165842</t>
+          <t>121339; 168042</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>222098; 289403</t>
+          <t>226434; 288140</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215427; 276784</t>
+          <t>216973; 279324</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>205847; 295542</t>
+          <t>248834; 311140</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46378</t>
+          <t>53955</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71064</t>
+          <t>80770</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11990; 31329</t>
+          <t>12661; 31412</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7223; 27102</t>
+          <t>7722; 27180</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8726; 26161</t>
+          <t>8477; 27032</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16283; 36402</t>
+          <t>16992; 39285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13953; 31564</t>
+          <t>14307; 31974</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15206; 34666</t>
+          <t>13658; 33206</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16584; 36209</t>
+          <t>15611; 36240</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34935; 59903</t>
+          <t>42533; 68528</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30899; 56196</t>
+          <t>30834; 57821</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26032; 52161</t>
+          <t>25478; 52375</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30118; 54935</t>
+          <t>28436; 53696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55198; 88643</t>
+          <t>64712; 99169</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187132</t>
+          <t>202105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>363931</t>
+          <t>401411</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>551063</t>
+          <t>603515</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>146756; 198797</t>
+          <t>148464; 198912</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>200811; 262456</t>
+          <t>199182; 259231</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>156583; 209605</t>
+          <t>158263; 208922</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141847; 214515</t>
+          <t>178012; 232677</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>254321; 320284</t>
+          <t>256407; 320052</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>458937; 543010</t>
+          <t>452980; 540161</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>343280; 417314</t>
+          <t>340570; 416385</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>295723; 405709</t>
+          <t>369502; 435370</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>416760; 498152</t>
+          <t>417963; 503940</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>671626; 780492</t>
+          <t>667567; 779420</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>512918; 607692</t>
+          <t>518275; 606367</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>478279; 605036</t>
+          <t>562723; 648209</t>
         </is>
       </c>
     </row>
